--- a/public/sap-reporting/expansion-150-downloads/EXT-PP06-01.xlsx
+++ b/public/sap-reporting/expansion-150-downloads/EXT-PP06-01.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Layout" sheetId="1" r:id="Rc61aec7a05674148"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Flat input" sheetId="2" r:id="R59136037dc55438b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fields" sheetId="3" r:id="R1f137810b9a1473c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Layout" sheetId="1" r:id="Rcba1822d746e4011"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Flat input" sheetId="2" r:id="Rddb73e51a0a34f69"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fields" sheetId="3" r:id="R0fcdc8062b3a48ce"/>
   </x:sheets>
 </x:workbook>
 </file>
